--- a/Canal Habana.xlsx
+++ b/Canal Habana.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-Lunes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-Martes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-Miércoles" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-Jueves" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-Viernes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-Sábado" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-Domingo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lunes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Martes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Miércoles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jueves" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Viernes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sábado" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domingo" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen TV" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,13 +32,29 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -67,9 +83,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,603 +475,610 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Programacion Lunes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
+      <c r="I2" s="2">
+        <f>1+1</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E3" s="1">
-        <f>IF(G3&lt;&gt;"",$I$2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="1">
-        <f>IF(G3&lt;&gt;"",TEXT(TIMEVALUE(E3)+IFERROR(VLOOKUP(G3,$A$4:$C$19,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de inicio</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de terminacion</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3">
-        <f>IF(G3&lt;&gt;"",IFERROR(VLOOKUP(G3,$A$4:$C$19,3,FALSE),""))</f>
-        <v/>
-      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Tipo calc</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E4" s="1">
-        <f>IF(G4&lt;&gt;"",F3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="1">
-        <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="E4" s="2">
+        <f>IF(G4&lt;&gt;"",TIME(HOUR($I$2),MINUTE($I$2),0),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2">
+        <f>IF(G4&lt;&gt;"",TEXT(TIME(HOUR(E4),MINUTE(E4),0)+IFERROR(VLOOKUP(G4,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
       <c r="H4">
-        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E5" s="1">
-        <f>IF(G5&lt;&gt;"",F4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="1">
-        <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="E5" s="2">
+        <f>IF(G5&lt;&gt;"",F4,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>IF(G5&lt;&gt;"",TEXT(TIME(HOUR(E5),MINUTE(E5),0)+IFERROR(VLOOKUP(G5,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
       <c r="H5">
-        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>REVISTA HOLA HABANA</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>revista</t>
         </is>
       </c>
-      <c r="E6" s="1">
-        <f>IF(G6&lt;&gt;"",F5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="1">
-        <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="E6" s="2">
+        <f>IF(G6&lt;&gt;"",F5,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(G6&lt;&gt;"",TEXT(TIME(HOUR(E6),MINUTE(E6),0)+IFERROR(VLOOKUP(G6,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>REVISTA HOLA HABANA</t>
         </is>
       </c>
       <c r="H6">
-        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>DÉCADAS MILAGROSAS</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E7" s="1">
-        <f>IF(G7&lt;&gt;"",F6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="1">
-        <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="E7" s="2">
+        <f>IF(G7&lt;&gt;"",F6,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>IF(G7&lt;&gt;"",TEXT(TIME(HOUR(E7),MINUTE(E7),0)+IFERROR(VLOOKUP(G7,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>DÉCADAS MILAGROSAS</t>
         </is>
       </c>
       <c r="H7">
-        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E8" s="1">
-        <f>IF(G8&lt;&gt;"",F7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="1">
-        <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="E8" s="2">
+        <f>IF(G8&lt;&gt;"",F7,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>IF(G8&lt;&gt;"",TEXT(TIME(HOUR(E8),MINUTE(E8),0)+IFERROR(VLOOKUP(G8,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
       <c r="H8">
-        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>POWER RANGERS</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>infantil</t>
         </is>
       </c>
-      <c r="E9" s="1">
-        <f>IF(G9&lt;&gt;"",F8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="1">
-        <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="E9" s="2">
+        <f>IF(G9&lt;&gt;"",F8,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(G9&lt;&gt;"",TEXT(TIME(HOUR(E9),MINUTE(E9),0)+IFERROR(VLOOKUP(G9,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>POWER RANGERS</t>
         </is>
       </c>
       <c r="H9">
-        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>CINECITO EN TV</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="E10" s="1">
-        <f>IF(G10&lt;&gt;"",F9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="1">
-        <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="E10" s="2">
+        <f>IF(G10&lt;&gt;"",F9,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2">
+        <f>IF(G10&lt;&gt;"",TEXT(TIME(HOUR(E10),MINUTE(E10),0)+IFERROR(VLOOKUP(G10,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>CINECITO EN TV</t>
         </is>
       </c>
       <c r="H10">
-        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS INFANTILES</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E11" s="1">
-        <f>IF(G11&lt;&gt;"",F10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="1">
-        <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="E11" s="2">
+        <f>IF(G11&lt;&gt;"",F10,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="2">
+        <f>IF(G11&lt;&gt;"",TEXT(TIME(HOUR(E11),MINUTE(E11),0)+IFERROR(VLOOKUP(G11,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS INFANTILES</t>
         </is>
       </c>
       <c r="H11">
-        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>VE Y MIRA</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="E12" s="1">
-        <f>IF(G12&lt;&gt;"",F11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="1">
-        <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="E12" s="2">
+        <f>IF(G12&lt;&gt;"",F11,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(G12&lt;&gt;"",TEXT(TIME(HOUR(E12),MINUTE(E12),0)+IFERROR(VLOOKUP(G12,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>VE Y MIRA</t>
         </is>
       </c>
       <c r="H12">
-        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>MÚSICA HABANA</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E13" s="1">
-        <f>IF(G13&lt;&gt;"",F12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="1">
-        <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="E13" s="2">
+        <f>IF(G13&lt;&gt;"",F12,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="2">
+        <f>IF(G13&lt;&gt;"",TEXT(TIME(HOUR(E13),MINUTE(E13),0)+IFERROR(VLOOKUP(G13,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>MÚSICA HABANA</t>
         </is>
       </c>
       <c r="H13">
-        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>HABANA COLECCIÓN</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E14" s="1">
-        <f>IF(G14&lt;&gt;"",F13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="1">
-        <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="E14" s="2">
+        <f>IF(G14&lt;&gt;"",F13,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="2">
+        <f>IF(G14&lt;&gt;"",TEXT(TIME(HOUR(E14),MINUTE(E14),0)+IFERROR(VLOOKUP(G14,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>HABANA COLECCIÓN</t>
         </is>
       </c>
       <c r="H14">
-        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>MÚSICA SÍ</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E15" s="1">
-        <f>IF(G15&lt;&gt;"",F14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="1">
-        <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="E15" s="2">
+        <f>IF(G15&lt;&gt;"",F14,"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="2">
+        <f>IF(G15&lt;&gt;"",TEXT(TIME(HOUR(E15),MINUTE(E15),0)+IFERROR(VLOOKUP(G15,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>MÚSICA SÍ</t>
         </is>
       </c>
       <c r="H15">
-        <f>IF(G15&lt;&gt;"",IFERROR(VLOOKUP(G15,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G15&lt;&gt;"",IFERROR(VLOOKUP(G15,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>D DISEÑO</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E16" s="1">
-        <f>IF(G16&lt;&gt;"",F15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="1">
-        <f>IF(G16&lt;&gt;"",TEXT(TIMEVALUE(E16)+IFERROR(VLOOKUP(G16,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="E16" s="2">
+        <f>IF(G16&lt;&gt;"",F15,"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="2">
+        <f>IF(G16&lt;&gt;"",TEXT(TIME(HOUR(E16),MINUTE(E16),0)+IFERROR(VLOOKUP(G16,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>D DISEÑO</t>
         </is>
       </c>
       <c r="H16">
-        <f>IF(G16&lt;&gt;"",IFERROR(VLOOKUP(G16,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G16&lt;&gt;"",IFERROR(VLOOKUP(G16,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>SIN PUNTOS SUSPENSIVOS</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>entrevista</t>
         </is>
       </c>
-      <c r="E17" s="1">
-        <f>IF(G17&lt;&gt;"",F16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="1">
-        <f>IF(G17&lt;&gt;"",TEXT(TIMEVALUE(E17)+IFERROR(VLOOKUP(G17,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="E17" s="2">
+        <f>IF(G17&lt;&gt;"",F16,"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="2">
+        <f>IF(G17&lt;&gt;"",TEXT(TIME(HOUR(E17),MINUTE(E17),0)+IFERROR(VLOOKUP(G17,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>SIN PUNTOS SUSPENSIVOS</t>
         </is>
       </c>
       <c r="H17">
-        <f>IF(G17&lt;&gt;"",IFERROR(VLOOKUP(G17,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G17&lt;&gt;"",IFERROR(VLOOKUP(G17,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="E18" s="1">
-        <f>IF(G18&lt;&gt;"",F17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="1">
-        <f>IF(G18&lt;&gt;"",TEXT(TIMEVALUE(E18)+IFERROR(VLOOKUP(G18,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="E18" s="2">
+        <f>IF(G18&lt;&gt;"",F17,"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="2">
+        <f>IF(G18&lt;&gt;"",TEXT(TIME(HOUR(E18),MINUTE(E18),0)+IFERROR(VLOOKUP(G18,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
       <c r="H18">
-        <f>IF(G18&lt;&gt;"",IFERROR(VLOOKUP(G18,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G18&lt;&gt;"",IFERROR(VLOOKUP(G18,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E19" s="1">
-        <f>IF(G19&lt;&gt;"",F18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="1">
-        <f>IF(G19&lt;&gt;"",TEXT(TIMEVALUE(E19)+IFERROR(VLOOKUP(G19,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="E19" s="2">
+        <f>IF(G19&lt;&gt;"",F18,"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="2">
+        <f>IF(G19&lt;&gt;"",TEXT(TIME(HOUR(E19),MINUTE(E19),0)+IFERROR(VLOOKUP(G19,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
       <c r="H19">
-        <f>IF(G19&lt;&gt;"",IFERROR(VLOOKUP(G19,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G19&lt;&gt;"",IFERROR(VLOOKUP(G19,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="E20" s="1">
-        <f>IF(G20&lt;&gt;"",F19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="1">
-        <f>IF(G20&lt;&gt;"",TEXT(TIMEVALUE(E20)+IFERROR(VLOOKUP(G20,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="E20" s="2">
+        <f>IF(G20&lt;&gt;"",F19,"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="2">
+        <f>IF(G20&lt;&gt;"",TEXT(TIME(HOUR(E20),MINUTE(E20),0)+IFERROR(VLOOKUP(G20,$A$4:$C$20,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
       <c r="H20">
-        <f>IF(G20&lt;&gt;"",IFERROR(VLOOKUP(G20,$A$4:$C$20,3,FALSE),""))</f>
+        <f>IF(G20&lt;&gt;"",IFERROR(VLOOKUP(G20,$A$4:$C$20,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1072,347 +1104,354 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Programacion Martes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
+      <c r="I2" s="2">
+        <f>1+1</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E3" s="1">
-        <f>IF(G3&lt;&gt;"",$I$2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="1">
-        <f>IF(G3&lt;&gt;"",TEXT(TIMEVALUE(E3)+IFERROR(VLOOKUP(G3,$A$4:$C$19,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de inicio</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de terminacion</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3">
-        <f>IF(G3&lt;&gt;"",IFERROR(VLOOKUP(G3,$A$4:$C$19,3,FALSE),""))</f>
-        <v/>
-      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Tipo calc</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TODO POP</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E4" s="1">
-        <f>IF(G4&lt;&gt;"",F3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="1">
-        <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="E4" s="2">
+        <f>IF(G4&lt;&gt;"",TIME(HOUR($I$2),MINUTE($I$2),0),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2">
+        <f>IF(G4&lt;&gt;"",TEXT(TIME(HOUR(E4),MINUTE(E4),0)+IFERROR(VLOOKUP(G4,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>TODO POP</t>
         </is>
       </c>
       <c r="H4">
-        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$12,3,FALSE),""))</f>
+        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$12,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>BREVES ESTACIONES</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E5" s="1">
-        <f>IF(G5&lt;&gt;"",F4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="1">
-        <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="E5" s="2">
+        <f>IF(G5&lt;&gt;"",F4,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>IF(G5&lt;&gt;"",TEXT(TIME(HOUR(E5),MINUTE(E5),0)+IFERROR(VLOOKUP(G5,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>BREVES ESTACIONES</t>
         </is>
       </c>
       <c r="H5">
-        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$12,3,FALSE),""))</f>
+        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$12,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SALUDARTE</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>salud</t>
         </is>
       </c>
-      <c r="E6" s="1">
-        <f>IF(G6&lt;&gt;"",F5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="1">
-        <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="E6" s="2">
+        <f>IF(G6&lt;&gt;"",F5,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(G6&lt;&gt;"",TEXT(TIME(HOUR(E6),MINUTE(E6),0)+IFERROR(VLOOKUP(G6,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>SALUDARTE</t>
         </is>
       </c>
       <c r="H6">
-        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$12,3,FALSE),""))</f>
+        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$12,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SECUENCIA</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E7" s="1">
-        <f>IF(G7&lt;&gt;"",F6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="1">
-        <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="E7" s="2">
+        <f>IF(G7&lt;&gt;"",F6,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>IF(G7&lt;&gt;"",TEXT(TIME(HOUR(E7),MINUTE(E7),0)+IFERROR(VLOOKUP(G7,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>SECUENCIA</t>
         </is>
       </c>
       <c r="H7">
-        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$12,3,FALSE),""))</f>
+        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$12,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>RITMO CLIP</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E8" s="1">
-        <f>IF(G8&lt;&gt;"",F7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="1">
-        <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="E8" s="2">
+        <f>IF(G8&lt;&gt;"",F7,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>IF(G8&lt;&gt;"",TEXT(TIME(HOUR(E8),MINUTE(E8),0)+IFERROR(VLOOKUP(G8,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>RITMO CLIP</t>
         </is>
       </c>
       <c r="H8">
-        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$12,3,FALSE),""))</f>
+        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$12,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>TRIANGULO DE LA CONFIANZA</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>entrevista</t>
         </is>
       </c>
-      <c r="E9" s="1">
-        <f>IF(G9&lt;&gt;"",F8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="1">
-        <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="E9" s="2">
+        <f>IF(G9&lt;&gt;"",F8,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(G9&lt;&gt;"",TEXT(TIME(HOUR(E9),MINUTE(E9),0)+IFERROR(VLOOKUP(G9,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>TRIANGULO DE LA CONFIANZA</t>
         </is>
       </c>
       <c r="H9">
-        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$12,3,FALSE),""))</f>
+        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$12,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="E10" s="1">
-        <f>IF(G10&lt;&gt;"",F9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="1">
-        <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="E10" s="2">
+        <f>IF(G10&lt;&gt;"",F9,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2">
+        <f>IF(G10&lt;&gt;"",TEXT(TIME(HOUR(E10),MINUTE(E10),0)+IFERROR(VLOOKUP(G10,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
       <c r="H10">
-        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$12,3,FALSE),""))</f>
+        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$12,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E11" s="1">
-        <f>IF(G11&lt;&gt;"",F10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="1">
-        <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="E11" s="2">
+        <f>IF(G11&lt;&gt;"",F10,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="2">
+        <f>IF(G11&lt;&gt;"",TEXT(TIME(HOUR(E11),MINUTE(E11),0)+IFERROR(VLOOKUP(G11,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
       <c r="H11">
-        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$12,3,FALSE),""))</f>
+        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$12,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="E12" s="1">
-        <f>IF(G12&lt;&gt;"",F11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="1">
-        <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="E12" s="2">
+        <f>IF(G12&lt;&gt;"",F11,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(G12&lt;&gt;"",TEXT(TIME(HOUR(E12),MINUTE(E12),0)+IFERROR(VLOOKUP(G12,$A$4:$C$12,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
       <c r="H12">
-        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$12,3,FALSE),""))</f>
+        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$12,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1438,283 +1477,290 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Programacion Miercoles</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
+      <c r="I2" s="2">
+        <f>1+1</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E3" s="1">
-        <f>IF(G3&lt;&gt;"",$I$2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="1">
-        <f>IF(G3&lt;&gt;"",TEXT(TIMEVALUE(E3)+IFERROR(VLOOKUP(G3,$A$4:$C$19,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de inicio</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de terminacion</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3">
-        <f>IF(G3&lt;&gt;"",IFERROR(VLOOKUP(G3,$A$4:$C$19,3,FALSE),""))</f>
-        <v/>
-      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Tipo calc</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>COSAS DEL CINE</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="E4" s="1">
-        <f>IF(G4&lt;&gt;"",F3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="1">
-        <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="E4" s="2">
+        <f>IF(G4&lt;&gt;"",TIME(HOUR($I$2),MINUTE($I$2),0),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2">
+        <f>IF(G4&lt;&gt;"",TEXT(TIME(HOUR(E4),MINUTE(E4),0)+IFERROR(VLOOKUP(G4,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>COSAS DEL CINE</t>
         </is>
       </c>
       <c r="H4">
-        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$10,3,FALSE),""))</f>
+        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$10,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>RITMO CLIP</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E5" s="1">
-        <f>IF(G5&lt;&gt;"",F4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="1">
-        <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="E5" s="2">
+        <f>IF(G5&lt;&gt;"",F4,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>IF(G5&lt;&gt;"",TEXT(TIME(HOUR(E5),MINUTE(E5),0)+IFERROR(VLOOKUP(G5,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>RITMO CLIP</t>
         </is>
       </c>
       <c r="H5">
-        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$10,3,FALSE),""))</f>
+        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$10,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>BANDA SONORA JUVENIL</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E6" s="1">
-        <f>IF(G6&lt;&gt;"",F5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="1">
-        <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="E6" s="2">
+        <f>IF(G6&lt;&gt;"",F5,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(G6&lt;&gt;"",TEXT(TIME(HOUR(E6),MINUTE(E6),0)+IFERROR(VLOOKUP(G6,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>BANDA SONORA JUVENIL</t>
         </is>
       </c>
       <c r="H6">
-        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$10,3,FALSE),""))</f>
+        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$10,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>VE Y MIRA</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="E7" s="1">
-        <f>IF(G7&lt;&gt;"",F6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="1">
-        <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="E7" s="2">
+        <f>IF(G7&lt;&gt;"",F6,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>IF(G7&lt;&gt;"",TEXT(TIME(HOUR(E7),MINUTE(E7),0)+IFERROR(VLOOKUP(G7,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>VE Y MIRA</t>
         </is>
       </c>
       <c r="H7">
-        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$10,3,FALSE),""))</f>
+        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$10,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>MÚSICA DEL MUNDO</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E8" s="1">
-        <f>IF(G8&lt;&gt;"",F7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="1">
-        <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="E8" s="2">
+        <f>IF(G8&lt;&gt;"",F7,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>IF(G8&lt;&gt;"",TEXT(TIME(HOUR(E8),MINUTE(E8),0)+IFERROR(VLOOKUP(G8,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>MÚSICA DEL MUNDO</t>
         </is>
       </c>
       <c r="H8">
-        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$10,3,FALSE),""))</f>
+        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$10,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E9" s="1">
-        <f>IF(G9&lt;&gt;"",F8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="1">
-        <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="E9" s="2">
+        <f>IF(G9&lt;&gt;"",F8,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(G9&lt;&gt;"",TEXT(TIME(HOUR(E9),MINUTE(E9),0)+IFERROR(VLOOKUP(G9,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
       <c r="H9">
-        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$10,3,FALSE),""))</f>
+        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$10,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>CINEMA HABANA</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="E10" s="1">
-        <f>IF(G10&lt;&gt;"",F9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="1">
-        <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="E10" s="2">
+        <f>IF(G10&lt;&gt;"",F9,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2">
+        <f>IF(G10&lt;&gt;"",TEXT(TIME(HOUR(E10),MINUTE(E10),0)+IFERROR(VLOOKUP(G10,$A$4:$C$10,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>CINEMA HABANA</t>
         </is>
       </c>
       <c r="H10">
-        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$10,3,FALSE),""))</f>
+        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$10,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1740,635 +1786,642 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Programacion Jueves</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
+      <c r="I2" s="2">
+        <f>1+1</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E3" s="1">
-        <f>IF(G3&lt;&gt;"",$I$2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="1">
-        <f>IF(G3&lt;&gt;"",TEXT(TIMEVALUE(E3)+IFERROR(VLOOKUP(G3,$A$4:$C$19,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de inicio</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de terminacion</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3">
-        <f>IF(G3&lt;&gt;"",IFERROR(VLOOKUP(G3,$A$4:$C$19,3,FALSE),""))</f>
-        <v/>
-      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Tipo calc</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E4" s="1">
-        <f>IF(G4&lt;&gt;"",F3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="1">
-        <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="E4" s="2">
+        <f>IF(G4&lt;&gt;"",TIME(HOUR($I$2),MINUTE($I$2),0),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2">
+        <f>IF(G4&lt;&gt;"",TEXT(TIME(HOUR(E4),MINUTE(E4),0)+IFERROR(VLOOKUP(G4,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
       <c r="H4">
-        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E5" s="1">
-        <f>IF(G5&lt;&gt;"",F4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="1">
-        <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="E5" s="2">
+        <f>IF(G5&lt;&gt;"",F4,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>IF(G5&lt;&gt;"",TEXT(TIME(HOUR(E5),MINUTE(E5),0)+IFERROR(VLOOKUP(G5,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
       <c r="H5">
-        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>REVISTA HOLA HABANA</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>revista</t>
         </is>
       </c>
-      <c r="E6" s="1">
-        <f>IF(G6&lt;&gt;"",F5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="1">
-        <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="E6" s="2">
+        <f>IF(G6&lt;&gt;"",F5,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(G6&lt;&gt;"",TEXT(TIME(HOUR(E6),MINUTE(E6),0)+IFERROR(VLOOKUP(G6,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>REVISTA HOLA HABANA</t>
         </is>
       </c>
       <c r="H6">
-        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SALUDARTE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>salud</t>
         </is>
       </c>
-      <c r="E7" s="1">
-        <f>IF(G7&lt;&gt;"",F6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="1">
-        <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="E7" s="2">
+        <f>IF(G7&lt;&gt;"",F6,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>IF(G7&lt;&gt;"",TEXT(TIME(HOUR(E7),MINUTE(E7),0)+IFERROR(VLOOKUP(G7,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>SALUDARTE</t>
         </is>
       </c>
       <c r="H7">
-        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>SECUENCIA</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E8" s="1">
-        <f>IF(G8&lt;&gt;"",F7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="1">
-        <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="E8" s="2">
+        <f>IF(G8&lt;&gt;"",F7,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>IF(G8&lt;&gt;"",TEXT(TIME(HOUR(E8),MINUTE(E8),0)+IFERROR(VLOOKUP(G8,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>SECUENCIA</t>
         </is>
       </c>
       <c r="H8">
-        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E9" s="1">
-        <f>IF(G9&lt;&gt;"",F8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="1">
-        <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="E9" s="2">
+        <f>IF(G9&lt;&gt;"",F8,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(G9&lt;&gt;"",TEXT(TIME(HOUR(E9),MINUTE(E9),0)+IFERROR(VLOOKUP(G9,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
       <c r="H9">
-        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>CAZADOR DE TROLES</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>infantil</t>
         </is>
       </c>
-      <c r="E10" s="1">
-        <f>IF(G10&lt;&gt;"",F9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="1">
-        <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="E10" s="2">
+        <f>IF(G10&lt;&gt;"",F9,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2">
+        <f>IF(G10&lt;&gt;"",TEXT(TIME(HOUR(E10),MINUTE(E10),0)+IFERROR(VLOOKUP(G10,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>CAZADOR DE TROLES</t>
         </is>
       </c>
       <c r="H10">
-        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>EL MUNDO DE CRAIG</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>animacion</t>
         </is>
       </c>
-      <c r="E11" s="1">
-        <f>IF(G11&lt;&gt;"",F10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="1">
-        <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="E11" s="2">
+        <f>IF(G11&lt;&gt;"",F10,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="2">
+        <f>IF(G11&lt;&gt;"",TEXT(TIME(HOUR(E11),MINUTE(E11),0)+IFERROR(VLOOKUP(G11,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>EL MUNDO DE CRAIG</t>
         </is>
       </c>
       <c r="H11">
-        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>ÁNIMA</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>animacion</t>
         </is>
       </c>
-      <c r="E12" s="1">
-        <f>IF(G12&lt;&gt;"",F11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="1">
-        <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="E12" s="2">
+        <f>IF(G12&lt;&gt;"",F11,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(G12&lt;&gt;"",TEXT(TIME(HOUR(E12),MINUTE(E12),0)+IFERROR(VLOOKUP(G12,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>ÁNIMA</t>
         </is>
       </c>
       <c r="H12">
-        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>PAPEL EN BLANCO</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E13" s="1">
-        <f>IF(G13&lt;&gt;"",F12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="1">
-        <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="E13" s="2">
+        <f>IF(G13&lt;&gt;"",F12,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="2">
+        <f>IF(G13&lt;&gt;"",TEXT(TIME(HOUR(E13),MINUTE(E13),0)+IFERROR(VLOOKUP(G13,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>PAPEL EN BLANCO</t>
         </is>
       </c>
       <c r="H13">
-        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>MÚSICA DEL MUNDO</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E14" s="1">
-        <f>IF(G14&lt;&gt;"",F13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="1">
-        <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="E14" s="2">
+        <f>IF(G14&lt;&gt;"",F13,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="2">
+        <f>IF(G14&lt;&gt;"",TEXT(TIME(HOUR(E14),MINUTE(E14),0)+IFERROR(VLOOKUP(G14,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>MÚSICA DEL MUNDO</t>
         </is>
       </c>
       <c r="H14">
-        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TRAVESÍA</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E15" s="1">
-        <f>IF(G15&lt;&gt;"",F14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="1">
-        <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="E15" s="2">
+        <f>IF(G15&lt;&gt;"",F14,"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="2">
+        <f>IF(G15&lt;&gt;"",TEXT(TIME(HOUR(E15),MINUTE(E15),0)+IFERROR(VLOOKUP(G15,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>TRAVESÍA</t>
         </is>
       </c>
       <c r="H15">
-        <f>IF(G15&lt;&gt;"",IFERROR(VLOOKUP(G15,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G15&lt;&gt;"",IFERROR(VLOOKUP(G15,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>DONDE VA LA HABANA</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E16" s="1">
-        <f>IF(G16&lt;&gt;"",F15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="1">
-        <f>IF(G16&lt;&gt;"",TEXT(TIMEVALUE(E16)+IFERROR(VLOOKUP(G16,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="E16" s="2">
+        <f>IF(G16&lt;&gt;"",F15,"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="2">
+        <f>IF(G16&lt;&gt;"",TEXT(TIME(HOUR(E16),MINUTE(E16),0)+IFERROR(VLOOKUP(G16,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>DONDE VA LA HABANA</t>
         </is>
       </c>
       <c r="H16">
-        <f>IF(G16&lt;&gt;"",IFERROR(VLOOKUP(G16,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G16&lt;&gt;"",IFERROR(VLOOKUP(G16,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>BANDA SONORA</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E17" s="1">
-        <f>IF(G17&lt;&gt;"",F16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="1">
-        <f>IF(G17&lt;&gt;"",TEXT(TIMEVALUE(E17)+IFERROR(VLOOKUP(G17,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="E17" s="2">
+        <f>IF(G17&lt;&gt;"",F16,"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="2">
+        <f>IF(G17&lt;&gt;"",TEXT(TIME(HOUR(E17),MINUTE(E17),0)+IFERROR(VLOOKUP(G17,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>BANDA SONORA</t>
         </is>
       </c>
       <c r="H17">
-        <f>IF(G17&lt;&gt;"",IFERROR(VLOOKUP(G17,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G17&lt;&gt;"",IFERROR(VLOOKUP(G17,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>ESTA ES MI PEÑA</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E18" s="1">
-        <f>IF(G18&lt;&gt;"",F17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="1">
-        <f>IF(G18&lt;&gt;"",TEXT(TIMEVALUE(E18)+IFERROR(VLOOKUP(G18,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="E18" s="2">
+        <f>IF(G18&lt;&gt;"",F17,"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="2">
+        <f>IF(G18&lt;&gt;"",TEXT(TIME(HOUR(E18),MINUTE(E18),0)+IFERROR(VLOOKUP(G18,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>ESTA ES MI PEÑA</t>
         </is>
       </c>
       <c r="H18">
-        <f>IF(G18&lt;&gt;"",IFERROR(VLOOKUP(G18,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G18&lt;&gt;"",IFERROR(VLOOKUP(G18,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="E19" s="1">
-        <f>IF(G19&lt;&gt;"",F18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="1">
-        <f>IF(G19&lt;&gt;"",TEXT(TIMEVALUE(E19)+IFERROR(VLOOKUP(G19,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="E19" s="2">
+        <f>IF(G19&lt;&gt;"",F18,"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="2">
+        <f>IF(G19&lt;&gt;"",TEXT(TIME(HOUR(E19),MINUTE(E19),0)+IFERROR(VLOOKUP(G19,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
       <c r="H19">
-        <f>IF(G19&lt;&gt;"",IFERROR(VLOOKUP(G19,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G19&lt;&gt;"",IFERROR(VLOOKUP(G19,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E20" s="1">
-        <f>IF(G20&lt;&gt;"",F19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="1">
-        <f>IF(G20&lt;&gt;"",TEXT(TIMEVALUE(E20)+IFERROR(VLOOKUP(G20,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="E20" s="2">
+        <f>IF(G20&lt;&gt;"",F19,"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="2">
+        <f>IF(G20&lt;&gt;"",TEXT(TIME(HOUR(E20),MINUTE(E20),0)+IFERROR(VLOOKUP(G20,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
       <c r="H20">
-        <f>IF(G20&lt;&gt;"",IFERROR(VLOOKUP(G20,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G20&lt;&gt;"",IFERROR(VLOOKUP(G20,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="E21" s="1">
-        <f>IF(G21&lt;&gt;"",F20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="1">
-        <f>IF(G21&lt;&gt;"",TEXT(TIMEVALUE(E21)+IFERROR(VLOOKUP(G21,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="E21" s="2">
+        <f>IF(G21&lt;&gt;"",F20,"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="2">
+        <f>IF(G21&lt;&gt;"",TEXT(TIME(HOUR(E21),MINUTE(E21),0)+IFERROR(VLOOKUP(G21,$A$4:$C$21,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
       <c r="H21">
-        <f>IF(G21&lt;&gt;"",IFERROR(VLOOKUP(G21,$A$4:$C$21,3,FALSE),""))</f>
+        <f>IF(G21&lt;&gt;"",IFERROR(VLOOKUP(G21,$A$4:$C$21,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2394,443 +2447,450 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Programacion Viernes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
+      <c r="I2" s="2">
+        <f>1+1</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E3" s="1">
-        <f>IF(G3&lt;&gt;"",$I$2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="1">
-        <f>IF(G3&lt;&gt;"",TEXT(TIMEVALUE(E3)+IFERROR(VLOOKUP(G3,$A$4:$C$19,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de inicio</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de terminacion</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3">
-        <f>IF(G3&lt;&gt;"",IFERROR(VLOOKUP(G3,$A$4:$C$19,3,FALSE),""))</f>
-        <v/>
-      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Tipo calc</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GEN HABANERO</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>documental</t>
         </is>
       </c>
-      <c r="E4" s="1">
-        <f>IF(G4&lt;&gt;"",F3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="1">
-        <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="E4" s="2">
+        <f>IF(G4&lt;&gt;"",TIME(HOUR($I$2),MINUTE($I$2),0),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2">
+        <f>IF(G4&lt;&gt;"",TEXT(TIME(HOUR(E4),MINUTE(E4),0)+IFERROR(VLOOKUP(G4,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>GEN HABANERO</t>
         </is>
       </c>
       <c r="H4">
-        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E5" s="1">
-        <f>IF(G5&lt;&gt;"",F4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="1">
-        <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="E5" s="2">
+        <f>IF(G5&lt;&gt;"",F4,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>IF(G5&lt;&gt;"",TEXT(TIME(HOUR(E5),MINUTE(E5),0)+IFERROR(VLOOKUP(G5,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
       <c r="H5">
-        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TIENE QUE VER</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="E6" s="1">
-        <f>IF(G6&lt;&gt;"",F5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="1">
-        <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="E6" s="2">
+        <f>IF(G6&lt;&gt;"",F5,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(G6&lt;&gt;"",TEXT(TIME(HOUR(E6),MINUTE(E6),0)+IFERROR(VLOOKUP(G6,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>TIENE QUE VER</t>
         </is>
       </c>
       <c r="H6">
-        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS INFANTILES</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E7" s="1">
-        <f>IF(G7&lt;&gt;"",F6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="1">
-        <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="E7" s="2">
+        <f>IF(G7&lt;&gt;"",F6,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>IF(G7&lt;&gt;"",TEXT(TIME(HOUR(E7),MINUTE(E7),0)+IFERROR(VLOOKUP(G7,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS INFANTILES</t>
         </is>
       </c>
       <c r="H7">
-        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ALGO ENTRE MANOS</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E8" s="1">
-        <f>IF(G8&lt;&gt;"",F7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="1">
-        <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="E8" s="2">
+        <f>IF(G8&lt;&gt;"",F7,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>IF(G8&lt;&gt;"",TEXT(TIME(HOUR(E8),MINUTE(E8),0)+IFERROR(VLOOKUP(G8,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>ALGO ENTRE MANOS</t>
         </is>
       </c>
       <c r="H8">
-        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>BREVES ESTACIONES</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E9" s="1">
-        <f>IF(G9&lt;&gt;"",F8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="1">
-        <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="E9" s="2">
+        <f>IF(G9&lt;&gt;"",F8,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(G9&lt;&gt;"",TEXT(TIME(HOUR(E9),MINUTE(E9),0)+IFERROR(VLOOKUP(G9,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>BREVES ESTACIONES</t>
         </is>
       </c>
       <c r="H9">
-        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>DÉCADAS MILAGROSAS</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E10" s="1">
-        <f>IF(G10&lt;&gt;"",F9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="1">
-        <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="E10" s="2">
+        <f>IF(G10&lt;&gt;"",F9,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2">
+        <f>IF(G10&lt;&gt;"",TEXT(TIME(HOUR(E10),MINUTE(E10),0)+IFERROR(VLOOKUP(G10,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>DÉCADAS MILAGROSAS</t>
         </is>
       </c>
       <c r="H10">
-        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SIN PUNTOS SUSPENSIVOS</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>entrevista</t>
         </is>
       </c>
-      <c r="E11" s="1">
-        <f>IF(G11&lt;&gt;"",F10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="1">
-        <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="E11" s="2">
+        <f>IF(G11&lt;&gt;"",F10,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="2">
+        <f>IF(G11&lt;&gt;"",TEXT(TIME(HOUR(E11),MINUTE(E11),0)+IFERROR(VLOOKUP(G11,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>SIN PUNTOS SUSPENSIVOS</t>
         </is>
       </c>
       <c r="H11">
-        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>YO BAILO</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E12" s="1">
-        <f>IF(G12&lt;&gt;"",F11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="1">
-        <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="E12" s="2">
+        <f>IF(G12&lt;&gt;"",F11,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(G12&lt;&gt;"",TEXT(TIME(HOUR(E12),MINUTE(E12),0)+IFERROR(VLOOKUP(G12,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>YO BAILO</t>
         </is>
       </c>
       <c r="H12">
-        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="E13" s="1">
-        <f>IF(G13&lt;&gt;"",F12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="1">
-        <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="E13" s="2">
+        <f>IF(G13&lt;&gt;"",F12,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="2">
+        <f>IF(G13&lt;&gt;"",TEXT(TIME(HOUR(E13),MINUTE(E13),0)+IFERROR(VLOOKUP(G13,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>NOVELA “LA NIETA ELEGIDA”</t>
         </is>
       </c>
       <c r="H13">
-        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E14" s="1">
-        <f>IF(G14&lt;&gt;"",F13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="1">
-        <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="E14" s="2">
+        <f>IF(G14&lt;&gt;"",F13,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="2">
+        <f>IF(G14&lt;&gt;"",TEXT(TIME(HOUR(E14),MINUTE(E14),0)+IFERROR(VLOOKUP(G14,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>HABANA NOTICIARIO</t>
         </is>
       </c>
       <c r="H14">
-        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="E15" s="1">
-        <f>IF(G15&lt;&gt;"",F14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="1">
-        <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="E15" s="2">
+        <f>IF(G15&lt;&gt;"",F14,"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="2">
+        <f>IF(G15&lt;&gt;"",TEXT(TIME(HOUR(E15),MINUTE(E15),0)+IFERROR(VLOOKUP(G15,$A$4:$C$15,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>SERIE “CRÍMENES MAYORES”</t>
         </is>
       </c>
       <c r="H15">
-        <f>IF(G15&lt;&gt;"",IFERROR(VLOOKUP(G15,$A$4:$C$15,3,FALSE),""))</f>
+        <f>IF(G15&lt;&gt;"",IFERROR(VLOOKUP(G15,$A$4:$C$15,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2856,507 +2916,514 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Programacion Sabado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
+      <c r="I2" s="2">
+        <f>1+1</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E3" s="1">
-        <f>IF(G3&lt;&gt;"",$I$2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="1">
-        <f>IF(G3&lt;&gt;"",TEXT(TIMEVALUE(E3)+IFERROR(VLOOKUP(G3,$A$4:$C$19,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de inicio</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de terminacion</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3">
-        <f>IF(G3&lt;&gt;"",IFERROR(VLOOKUP(G3,$A$4:$C$19,3,FALSE),""))</f>
-        <v/>
-      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Tipo calc</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E4" s="1">
-        <f>IF(G4&lt;&gt;"",F3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="1">
-        <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="E4" s="2">
+        <f>IF(G4&lt;&gt;"",TIME(HOUR($I$2),MINUTE($I$2),0),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2">
+        <f>IF(G4&lt;&gt;"",TEXT(TIME(HOUR(E4),MINUTE(E4),0)+IFERROR(VLOOKUP(G4,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
       <c r="H4">
-        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E5" s="1">
-        <f>IF(G5&lt;&gt;"",F4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="1">
-        <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="E5" s="2">
+        <f>IF(G5&lt;&gt;"",F4,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>IF(G5&lt;&gt;"",TEXT(TIME(HOUR(E5),MINUTE(E5),0)+IFERROR(VLOOKUP(G5,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
       <c r="H5">
-        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CUENTAS VERDE LIMÓN</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>infantil</t>
         </is>
       </c>
-      <c r="E6" s="1">
-        <f>IF(G6&lt;&gt;"",F5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="1">
-        <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="E6" s="2">
+        <f>IF(G6&lt;&gt;"",F5,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(G6&lt;&gt;"",TEXT(TIME(HOUR(E6),MINUTE(E6),0)+IFERROR(VLOOKUP(G6,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>CUENTAS VERDE LIMÓN</t>
         </is>
       </c>
       <c r="H6">
-        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>BANDA SONORA JUVENIL</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="E7" s="1">
-        <f>IF(G7&lt;&gt;"",F6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="1">
-        <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="E7" s="2">
+        <f>IF(G7&lt;&gt;"",F6,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>IF(G7&lt;&gt;"",TEXT(TIME(HOUR(E7),MINUTE(E7),0)+IFERROR(VLOOKUP(G7,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>BANDA SONORA JUVENIL</t>
         </is>
       </c>
       <c r="H7">
-        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TRAVESÍA</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E8" s="1">
-        <f>IF(G8&lt;&gt;"",F7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="1">
-        <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="E8" s="2">
+        <f>IF(G8&lt;&gt;"",F7,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>IF(G8&lt;&gt;"",TEXT(TIME(HOUR(E8),MINUTE(E8),0)+IFERROR(VLOOKUP(G8,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>TRAVESÍA</t>
         </is>
       </c>
       <c r="H8">
-        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>TODO POP</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E9" s="1">
-        <f>IF(G9&lt;&gt;"",F8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="1">
-        <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="E9" s="2">
+        <f>IF(G9&lt;&gt;"",F8,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(G9&lt;&gt;"",TEXT(TIME(HOUR(E9),MINUTE(E9),0)+IFERROR(VLOOKUP(G9,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>TODO POP</t>
         </is>
       </c>
       <c r="H9">
-        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>SERIE JUVENIL “SABRINA, LA BRUJA ADOLESCENTE”</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>ficción</t>
         </is>
       </c>
-      <c r="E10" s="1">
-        <f>IF(G10&lt;&gt;"",F9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="1">
-        <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="E10" s="2">
+        <f>IF(G10&lt;&gt;"",F9,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2">
+        <f>IF(G10&lt;&gt;"",TEXT(TIME(HOUR(E10),MINUTE(E10),0)+IFERROR(VLOOKUP(G10,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>SERIE JUVENIL “SABRINA, LA BRUJA ADOLESCENTE”</t>
         </is>
       </c>
       <c r="H10">
-        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>LIBRE ACCESO</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E11" s="1">
-        <f>IF(G11&lt;&gt;"",F10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="1">
-        <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="E11" s="2">
+        <f>IF(G11&lt;&gt;"",F10,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="2">
+        <f>IF(G11&lt;&gt;"",TEXT(TIME(HOUR(E11),MINUTE(E11),0)+IFERROR(VLOOKUP(G11,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>LIBRE ACCESO</t>
         </is>
       </c>
       <c r="H11">
-        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>JUGADA PERFECTA</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>deporte</t>
         </is>
       </c>
-      <c r="E12" s="1">
-        <f>IF(G12&lt;&gt;"",F11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="1">
-        <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="E12" s="2">
+        <f>IF(G12&lt;&gt;"",F11,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(G12&lt;&gt;"",TEXT(TIME(HOUR(E12),MINUTE(E12),0)+IFERROR(VLOOKUP(G12,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>JUGADA PERFECTA</t>
         </is>
       </c>
       <c r="H12">
-        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>QUE LA MÚSICA NO FALTE</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E13" s="1">
-        <f>IF(G13&lt;&gt;"",F12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="1">
-        <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="E13" s="2">
+        <f>IF(G13&lt;&gt;"",F12,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="2">
+        <f>IF(G13&lt;&gt;"",TEXT(TIME(HOUR(E13),MINUTE(E13),0)+IFERROR(VLOOKUP(G13,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>QUE LA MÚSICA NO FALTE</t>
         </is>
       </c>
       <c r="H13">
-        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>COSAS DEL CINE</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="E14" s="1">
-        <f>IF(G14&lt;&gt;"",F13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="1">
-        <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="E14" s="2">
+        <f>IF(G14&lt;&gt;"",F13,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="2">
+        <f>IF(G14&lt;&gt;"",TEXT(TIME(HOUR(E14),MINUTE(E14),0)+IFERROR(VLOOKUP(G14,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>COSAS DEL CINE</t>
         </is>
       </c>
       <c r="H14">
-        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>MÚSICA HABANA</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E15" s="1">
-        <f>IF(G15&lt;&gt;"",F14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="1">
-        <f>IF(G15&lt;&gt;"",TEXT(TIMEVALUE(E15)+IFERROR(VLOOKUP(G15,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="E15" s="2">
+        <f>IF(G15&lt;&gt;"",F14,"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="2">
+        <f>IF(G15&lt;&gt;"",TEXT(TIME(HOUR(E15),MINUTE(E15),0)+IFERROR(VLOOKUP(G15,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>MÚSICA HABANA</t>
         </is>
       </c>
       <c r="H15">
-        <f>IF(G15&lt;&gt;"",IFERROR(VLOOKUP(G15,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G15&lt;&gt;"",IFERROR(VLOOKUP(G15,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>X DISTANTE</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>animacion</t>
         </is>
       </c>
-      <c r="E16" s="1">
-        <f>IF(G16&lt;&gt;"",F15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="1">
-        <f>IF(G16&lt;&gt;"",TEXT(TIMEVALUE(E16)+IFERROR(VLOOKUP(G16,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="E16" s="2">
+        <f>IF(G16&lt;&gt;"",F15,"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="2">
+        <f>IF(G16&lt;&gt;"",TEXT(TIME(HOUR(E16),MINUTE(E16),0)+IFERROR(VLOOKUP(G16,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>X DISTANTE</t>
         </is>
       </c>
       <c r="H16">
-        <f>IF(G16&lt;&gt;"",IFERROR(VLOOKUP(G16,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G16&lt;&gt;"",IFERROR(VLOOKUP(G16,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>MÚSICA SI</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E17" s="1">
-        <f>IF(G17&lt;&gt;"",F16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="1">
-        <f>IF(G17&lt;&gt;"",TEXT(TIMEVALUE(E17)+IFERROR(VLOOKUP(G17,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="E17" s="2">
+        <f>IF(G17&lt;&gt;"",F16,"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="2">
+        <f>IF(G17&lt;&gt;"",TEXT(TIME(HOUR(E17),MINUTE(E17),0)+IFERROR(VLOOKUP(G17,$A$4:$C$17,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>MÚSICA SI</t>
         </is>
       </c>
       <c r="H17">
-        <f>IF(G17&lt;&gt;"",IFERROR(VLOOKUP(G17,$A$4:$C$17,3,FALSE),""))</f>
+        <f>IF(G17&lt;&gt;"",IFERROR(VLOOKUP(G17,$A$4:$C$17,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3382,411 +3449,418 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Programacion Domingo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Hora inicio 1ra fila</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
+      <c r="I2" s="2">
+        <f>1+1</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Duracion (min)</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E3" s="1">
-        <f>IF(G3&lt;&gt;"",$I$2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="1">
-        <f>IF(G3&lt;&gt;"",TEXT(TIMEVALUE(E3)+IFERROR(VLOOKUP(G3,$A$4:$C$19,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de inicio</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Hora de terminacion</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Programa</t>
         </is>
       </c>
-      <c r="H3">
-        <f>IF(G3&lt;&gt;"",IFERROR(VLOOKUP(G3,$A$4:$C$19,3,FALSE),""))</f>
-        <v/>
-      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Tipo calc</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E4" s="1">
-        <f>IF(G4&lt;&gt;"",F3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="1">
-        <f>IF(G4&lt;&gt;"",TEXT(TIMEVALUE(E4)+IFERROR(VLOOKUP(G4,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="E4" s="2">
+        <f>IF(G4&lt;&gt;"",TIME(HOUR($I$2),MINUTE($I$2),0),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2">
+        <f>IF(G4&lt;&gt;"",TEXT(TIME(HOUR(E4),MINUTE(E4),0)+IFERROR(VLOOKUP(G4,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>EL TIEMPO Y LA MEMORIA</t>
         </is>
       </c>
       <c r="H4">
-        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G4&lt;&gt;"",IFERROR(VLOOKUP(G4,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>informativo</t>
         </is>
       </c>
-      <c r="E5" s="1">
-        <f>IF(G5&lt;&gt;"",F4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="1">
-        <f>IF(G5&lt;&gt;"",TEXT(TIMEVALUE(E5)+IFERROR(VLOOKUP(G5,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="E5" s="2">
+        <f>IF(G5&lt;&gt;"",F4,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>IF(G5&lt;&gt;"",TEXT(TIME(HOUR(E5),MINUTE(E5),0)+IFERROR(VLOOKUP(G5,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
         </is>
       </c>
       <c r="H5">
-        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G5&lt;&gt;"",IFERROR(VLOOKUP(G5,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CANAL HABANA DEPORTES</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>deporte</t>
         </is>
       </c>
-      <c r="E6" s="1">
-        <f>IF(G6&lt;&gt;"",F5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="1">
-        <f>IF(G6&lt;&gt;"",TEXT(TIMEVALUE(E6)+IFERROR(VLOOKUP(G6,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="E6" s="2">
+        <f>IF(G6&lt;&gt;"",F5,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(G6&lt;&gt;"",TEXT(TIME(HOUR(E6),MINUTE(E6),0)+IFERROR(VLOOKUP(G6,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>CANAL HABANA DEPORTES</t>
         </is>
       </c>
       <c r="H6">
-        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G6&lt;&gt;"",IFERROR(VLOOKUP(G6,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>LATINOS</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E7" s="1">
-        <f>IF(G7&lt;&gt;"",F6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="1">
-        <f>IF(G7&lt;&gt;"",TEXT(TIMEVALUE(E7)+IFERROR(VLOOKUP(G7,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="E7" s="2">
+        <f>IF(G7&lt;&gt;"",F6,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>IF(G7&lt;&gt;"",TEXT(TIME(HOUR(E7),MINUTE(E7),0)+IFERROR(VLOOKUP(G7,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>LATINOS</t>
         </is>
       </c>
       <c r="H7">
-        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G7&lt;&gt;"",IFERROR(VLOOKUP(G7,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>PAPEL EN BLANCO</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E8" s="1">
-        <f>IF(G8&lt;&gt;"",F7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="1">
-        <f>IF(G8&lt;&gt;"",TEXT(TIMEVALUE(E8)+IFERROR(VLOOKUP(G8,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="E8" s="2">
+        <f>IF(G8&lt;&gt;"",F7,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>IF(G8&lt;&gt;"",TEXT(TIME(HOUR(E8),MINUTE(E8),0)+IFERROR(VLOOKUP(G8,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>PAPEL EN BLANCO</t>
         </is>
       </c>
       <c r="H8">
-        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G8&lt;&gt;"",IFERROR(VLOOKUP(G8,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>ALGO ENTRE MANOS</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="E9" s="1">
-        <f>IF(G9&lt;&gt;"",F8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="1">
-        <f>IF(G9&lt;&gt;"",TEXT(TIMEVALUE(E9)+IFERROR(VLOOKUP(G9,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="E9" s="2">
+        <f>IF(G9&lt;&gt;"",F8,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(G9&lt;&gt;"",TEXT(TIME(HOUR(E9),MINUTE(E9),0)+IFERROR(VLOOKUP(G9,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>ALGO ENTRE MANOS</t>
         </is>
       </c>
       <c r="H9">
-        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G9&lt;&gt;"",IFERROR(VLOOKUP(G9,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>VERDE HABANA</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>documental</t>
         </is>
       </c>
-      <c r="E10" s="1">
-        <f>IF(G10&lt;&gt;"",F9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="1">
-        <f>IF(G10&lt;&gt;"",TEXT(TIMEVALUE(E10)+IFERROR(VLOOKUP(G10,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="E10" s="2">
+        <f>IF(G10&lt;&gt;"",F9,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2">
+        <f>IF(G10&lt;&gt;"",TEXT(TIME(HOUR(E10),MINUTE(E10),0)+IFERROR(VLOOKUP(G10,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>VERDE HABANA</t>
         </is>
       </c>
       <c r="H10">
-        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G10&lt;&gt;"",IFERROR(VLOOKUP(G10,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>GEN HABANERO</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>documental</t>
         </is>
       </c>
-      <c r="E11" s="1">
-        <f>IF(G11&lt;&gt;"",F10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="1">
-        <f>IF(G11&lt;&gt;"",TEXT(TIMEVALUE(E11)+IFERROR(VLOOKUP(G11,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="E11" s="2">
+        <f>IF(G11&lt;&gt;"",F10,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="2">
+        <f>IF(G11&lt;&gt;"",TEXT(TIME(HOUR(E11),MINUTE(E11),0)+IFERROR(VLOOKUP(G11,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>GEN HABANERO</t>
         </is>
       </c>
       <c r="H11">
-        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G11&lt;&gt;"",IFERROR(VLOOKUP(G11,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TRIANGULO DE LA CONFIANZA</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>entrevista</t>
         </is>
       </c>
-      <c r="E12" s="1">
-        <f>IF(G12&lt;&gt;"",F11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="1">
-        <f>IF(G12&lt;&gt;"",TEXT(TIMEVALUE(E12)+IFERROR(VLOOKUP(G12,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="E12" s="2">
+        <f>IF(G12&lt;&gt;"",F11,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(G12&lt;&gt;"",TEXT(TIME(HOUR(E12),MINUTE(E12),0)+IFERROR(VLOOKUP(G12,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>TRIANGULO DE LA CONFIANZA</t>
         </is>
       </c>
       <c r="H12">
-        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G12&lt;&gt;"",IFERROR(VLOOKUP(G12,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>BANDA SONORA</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>musical</t>
         </is>
       </c>
-      <c r="E13" s="1">
-        <f>IF(G13&lt;&gt;"",F12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="1">
-        <f>IF(G13&lt;&gt;"",TEXT(TIMEVALUE(E13)+IFERROR(VLOOKUP(G13,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="E13" s="2">
+        <f>IF(G13&lt;&gt;"",F12,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="2">
+        <f>IF(G13&lt;&gt;"",TEXT(TIME(HOUR(E13),MINUTE(E13),0)+IFERROR(VLOOKUP(G13,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>BANDA SONORA</t>
         </is>
       </c>
       <c r="H13">
-        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G13&lt;&gt;"",IFERROR(VLOOKUP(G13,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>CINE +</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>cine</t>
         </is>
       </c>
-      <c r="E14" s="1">
-        <f>IF(G14&lt;&gt;"",F13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="1">
-        <f>IF(G14&lt;&gt;"",TEXT(TIMEVALUE(E14)+IFERROR(VLOOKUP(G14,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="E14" s="2">
+        <f>IF(G14&lt;&gt;"",F13,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="2">
+        <f>IF(G14&lt;&gt;"",TEXT(TIME(HOUR(E14),MINUTE(E14),0)+IFERROR(VLOOKUP(G14,$A$4:$C$14,2,FALSE),0)/1440,"hh:mm"),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>CINE +</t>
         </is>
       </c>
       <c r="H14">
-        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$14,3,FALSE),""))</f>
+        <f>IF(G14&lt;&gt;"",IFERROR(VLOOKUP(G14,$A$4:$C$14,3,FALSE),""),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3810,186 +3884,186 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Día</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Programas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Inicio</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Fin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Tipos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Públicos</t>
         </is>
       </c>
-      <c r="H1" s="1" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>242</v>
       </c>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="D7" s="1" t="n"/>
-      <c r="E7" s="1" t="n"/>
-      <c r="F7" s="1" t="n"/>
-      <c r="G7" s="1" t="n"/>
-      <c r="H7" s="1" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>1315</v>
       </c>
-      <c r="D8" s="1" t="n"/>
-      <c r="E8" s="1" t="n"/>
-      <c r="F8" s="1" t="n"/>
-      <c r="G8" s="1" t="n"/>
-      <c r="H8" s="1" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>3717</v>
       </c>
-      <c r="D9" s="1" t="n"/>
-      <c r="E9" s="1" t="n"/>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="inlineStr">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Canal Habana</t>
         </is>
